--- a/data/gravel/Esker Lorax Ti 2025.xlsx
+++ b/data/gravel/Esker Lorax Ti 2025.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10810"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10921"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/walker/Documents/Github/Bike Geometry Project/data/hardtail/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/walker/Documents/Github/Bike Geometry Project/data/gravel/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{70212262-8244-3548-B303-4282090301BB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1156DFFA-A0AC-DF4B-A277-C7E6CA27426C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="7380" yWindow="500" windowWidth="20520" windowHeight="17080" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -344,9 +344,6 @@
     <t>rigid</t>
   </si>
   <si>
-    <t>threaded</t>
-  </si>
-  <si>
     <t>no</t>
   </si>
   <si>
@@ -363,6 +360,9 @@
   </si>
   <si>
     <t>S4/XL</t>
+  </si>
+  <si>
+    <t>threaded 73</t>
   </si>
 </sst>
 </file>
@@ -817,16 +817,16 @@
         <v>8</v>
       </c>
       <c r="C8" s="3" t="s">
+        <v>105</v>
+      </c>
+      <c r="D8" s="3" t="s">
         <v>106</v>
       </c>
-      <c r="D8" s="3" t="s">
+      <c r="E8" s="3" t="s">
         <v>107</v>
       </c>
-      <c r="E8" s="3" t="s">
+      <c r="F8" s="3" t="s">
         <v>108</v>
-      </c>
-      <c r="F8" s="3" t="s">
-        <v>109</v>
       </c>
     </row>
     <row r="9" spans="1:6">
@@ -1406,7 +1406,7 @@
         <v>47</v>
       </c>
       <c r="B50" s="1" t="s">
-        <v>103</v>
+        <v>109</v>
       </c>
     </row>
     <row r="51" spans="1:2">
@@ -1427,7 +1427,7 @@
         <v>50</v>
       </c>
       <c r="B53" s="1" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
     </row>
     <row r="54" spans="1:2">
@@ -1557,7 +1557,7 @@
         <v>70</v>
       </c>
       <c r="B73" s="1" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
     </row>
   </sheetData>

--- a/data/gravel/Esker Lorax Ti 2025.xlsx
+++ b/data/gravel/Esker Lorax Ti 2025.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10921"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10928"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/walker/Documents/Github/Bike Geometry Project/data/gravel/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1156DFFA-A0AC-DF4B-A277-C7E6CA27426C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{746C2D9A-CFAC-994F-8073-D9C74B49FC6D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="7380" yWindow="500" windowWidth="20520" windowHeight="17080" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="115" uniqueCount="110">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="115" uniqueCount="111">
   <si>
     <t>brand</t>
   </si>
@@ -341,9 +341,6 @@
     <t>frame_weight</t>
   </si>
   <si>
-    <t>rigid</t>
-  </si>
-  <si>
     <t>no</t>
   </si>
   <si>
@@ -363,6 +360,12 @@
   </si>
   <si>
     <t>threaded 73</t>
+  </si>
+  <si>
+    <t>effectively equal to rigid fork of this length</t>
+  </si>
+  <si>
+    <t>suspension</t>
   </si>
 </sst>
 </file>
@@ -817,16 +820,16 @@
         <v>8</v>
       </c>
       <c r="C8" s="3" t="s">
+        <v>104</v>
+      </c>
+      <c r="D8" s="3" t="s">
         <v>105</v>
       </c>
-      <c r="D8" s="3" t="s">
+      <c r="E8" s="3" t="s">
         <v>106</v>
       </c>
-      <c r="E8" s="3" t="s">
+      <c r="F8" s="3" t="s">
         <v>107</v>
-      </c>
-      <c r="F8" s="3" t="s">
-        <v>108</v>
       </c>
     </row>
     <row r="9" spans="1:6">
@@ -1047,6 +1050,9 @@
       </c>
       <c r="F19" s="7">
         <v>495</v>
+      </c>
+      <c r="G19" s="1" t="s">
+        <v>109</v>
       </c>
     </row>
     <row r="20" spans="1:7">
@@ -1321,7 +1327,7 @@
         <v>75</v>
       </c>
       <c r="B38" s="1" t="s">
-        <v>102</v>
+        <v>110</v>
       </c>
     </row>
     <row r="39" spans="1:7">
@@ -1371,8 +1377,8 @@
       <c r="A45" t="s">
         <v>42</v>
       </c>
-      <c r="B45" s="1" t="s">
-        <v>37</v>
+      <c r="B45" s="1">
+        <v>120</v>
       </c>
     </row>
     <row r="46" spans="1:7">
@@ -1406,7 +1412,7 @@
         <v>47</v>
       </c>
       <c r="B50" s="1" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
     </row>
     <row r="51" spans="1:2">
@@ -1427,7 +1433,7 @@
         <v>50</v>
       </c>
       <c r="B53" s="1" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
     </row>
     <row r="54" spans="1:2">
@@ -1557,7 +1563,7 @@
         <v>70</v>
       </c>
       <c r="B73" s="1" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
     </row>
   </sheetData>

--- a/data/gravel/Esker Lorax Ti 2025.xlsx
+++ b/data/gravel/Esker Lorax Ti 2025.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10928"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11003"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/walker/Documents/Github/Bike Geometry Project/data/gravel/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{746C2D9A-CFAC-994F-8073-D9C74B49FC6D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BC46BFB4-C95F-354D-A234-66964349BB14}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="7380" yWindow="500" windowWidth="20520" windowHeight="17080" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="115" uniqueCount="111">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="116" uniqueCount="112">
   <si>
     <t>brand</t>
   </si>
@@ -366,6 +366,9 @@
   </si>
   <si>
     <t>suspension</t>
+  </si>
+  <si>
+    <t>https://eskercycles.com/cdn/shop/files/Lorax_Rigid_Ti_3_5_25_0013_1.jpg?v=1741577688&amp;width=3840</t>
   </si>
 </sst>
 </file>
@@ -801,6 +804,11 @@
         <v>78</v>
       </c>
     </row>
+    <row r="6" spans="1:6">
+      <c r="B6" t="s">
+        <v>111</v>
+      </c>
+    </row>
     <row r="7" spans="1:6" ht="22">
       <c r="A7" t="s">
         <v>6</v>

--- a/data/gravel/Esker Lorax Ti 2025.xlsx
+++ b/data/gravel/Esker Lorax Ti 2025.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11003"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11012"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/walker/Documents/Github/Bike Geometry Project/data/gravel/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BC46BFB4-C95F-354D-A234-66964349BB14}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5C01D7A6-873A-DF41-A874-931A2302258E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="7380" yWindow="500" windowWidth="20520" windowHeight="17080" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="116" uniqueCount="112">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="118" uniqueCount="114">
   <si>
     <t>brand</t>
   </si>
@@ -344,9 +344,6 @@
     <t>no</t>
   </si>
   <si>
-    <t>us</t>
-  </si>
-  <si>
     <t>S1/SM</t>
   </si>
   <si>
@@ -369,6 +366,15 @@
   </si>
   <si>
     <t>https://eskercycles.com/cdn/shop/files/Lorax_Rigid_Ti_3_5_25_0013_1.jpg?v=1741577688&amp;width=3840</t>
+  </si>
+  <si>
+    <t>location</t>
+  </si>
+  <si>
+    <t>Minneapolis, Minnesota, USA</t>
+  </si>
+  <si>
+    <t>USD</t>
   </si>
 </sst>
 </file>
@@ -758,7 +764,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:G73"/>
+  <dimension ref="A1:G74"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="20"/>
   <cols>
     <col min="1" max="2" width="19.6640625" customWidth="1"/>
@@ -806,7 +812,7 @@
     </row>
     <row r="6" spans="1:6">
       <c r="B6" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
     </row>
     <row r="7" spans="1:6" ht="22">
@@ -828,16 +834,16 @@
         <v>8</v>
       </c>
       <c r="C8" s="3" t="s">
+        <v>103</v>
+      </c>
+      <c r="D8" s="3" t="s">
         <v>104</v>
       </c>
-      <c r="D8" s="3" t="s">
+      <c r="E8" s="3" t="s">
         <v>105</v>
       </c>
-      <c r="E8" s="3" t="s">
+      <c r="F8" s="3" t="s">
         <v>106</v>
-      </c>
-      <c r="F8" s="3" t="s">
-        <v>107</v>
       </c>
     </row>
     <row r="9" spans="1:6">
@@ -1060,7 +1066,7 @@
         <v>495</v>
       </c>
       <c r="G19" s="1" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
     </row>
     <row r="20" spans="1:7">
@@ -1335,7 +1341,7 @@
         <v>75</v>
       </c>
       <c r="B38" s="1" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
     </row>
     <row r="39" spans="1:7">
@@ -1420,7 +1426,7 @@
         <v>47</v>
       </c>
       <c r="B50" s="1" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
     </row>
     <row r="51" spans="1:2">
@@ -1571,7 +1577,15 @@
         <v>70</v>
       </c>
       <c r="B73" s="1" t="s">
-        <v>103</v>
+        <v>113</v>
+      </c>
+    </row>
+    <row r="74" spans="1:2">
+      <c r="A74" t="s">
+        <v>111</v>
+      </c>
+      <c r="B74" t="s">
+        <v>112</v>
       </c>
     </row>
   </sheetData>

--- a/data/gravel/Esker Lorax Ti 2025.xlsx
+++ b/data/gravel/Esker Lorax Ti 2025.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11012"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11026"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/walker/Documents/Github/Bike Geometry Project/data/gravel/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5C01D7A6-873A-DF41-A874-931A2302258E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{634AE11E-D668-FE4E-94B1-954B54314412}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="7380" yWindow="500" windowWidth="20520" windowHeight="17080" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="118" uniqueCount="114">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="124" uniqueCount="120">
   <si>
     <t>brand</t>
   </si>
@@ -375,6 +375,24 @@
   </si>
   <si>
     <t>USD</t>
+  </si>
+  <si>
+    <t>head_tube_d</t>
+  </si>
+  <si>
+    <t>headset_upper</t>
+  </si>
+  <si>
+    <t>headset_lower</t>
+  </si>
+  <si>
+    <t>fork_steerer</t>
+  </si>
+  <si>
+    <t>fork_steerer_d</t>
+  </si>
+  <si>
+    <t>fork_material</t>
   </si>
 </sst>
 </file>
@@ -764,7 +782,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:G74"/>
+  <dimension ref="A1:G80"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="20"/>
   <cols>
     <col min="1" max="2" width="19.6640625" customWidth="1"/>
@@ -1423,168 +1441,198 @@
     </row>
     <row r="50" spans="1:2">
       <c r="A50" t="s">
-        <v>47</v>
-      </c>
-      <c r="B50" s="1" t="s">
-        <v>107</v>
+        <v>114</v>
       </c>
     </row>
     <row r="51" spans="1:2">
       <c r="A51" t="s">
-        <v>48</v>
+        <v>115</v>
       </c>
     </row>
     <row r="52" spans="1:2">
       <c r="A52" t="s">
-        <v>49</v>
-      </c>
-      <c r="B52">
-        <v>31.6</v>
+        <v>116</v>
       </c>
     </row>
     <row r="53" spans="1:2">
       <c r="A53" t="s">
-        <v>50</v>
-      </c>
-      <c r="B53" s="1" t="s">
-        <v>102</v>
+        <v>117</v>
       </c>
     </row>
     <row r="54" spans="1:2">
       <c r="A54" t="s">
-        <v>51</v>
-      </c>
-      <c r="B54">
-        <v>38</v>
+        <v>118</v>
       </c>
     </row>
     <row r="55" spans="1:2">
       <c r="A55" t="s">
-        <v>52</v>
+        <v>119</v>
       </c>
     </row>
     <row r="56" spans="1:2">
       <c r="A56" t="s">
-        <v>53</v>
+        <v>47</v>
+      </c>
+      <c r="B56" s="1" t="s">
+        <v>107</v>
       </c>
     </row>
     <row r="57" spans="1:2">
       <c r="A57" t="s">
-        <v>54</v>
+        <v>48</v>
       </c>
     </row>
     <row r="58" spans="1:2">
       <c r="A58" t="s">
-        <v>55</v>
+        <v>49</v>
+      </c>
+      <c r="B58">
+        <v>31.6</v>
       </c>
     </row>
     <row r="59" spans="1:2">
       <c r="A59" t="s">
-        <v>56</v>
+        <v>50</v>
+      </c>
+      <c r="B59" s="1" t="s">
+        <v>102</v>
       </c>
     </row>
     <row r="60" spans="1:2">
       <c r="A60" t="s">
-        <v>57</v>
-      </c>
-      <c r="B60" s="1" t="s">
-        <v>37</v>
+        <v>51</v>
+      </c>
+      <c r="B60">
+        <v>38</v>
       </c>
     </row>
     <row r="61" spans="1:2">
       <c r="A61" t="s">
-        <v>58</v>
+        <v>52</v>
       </c>
     </row>
     <row r="62" spans="1:2">
       <c r="A62" t="s">
-        <v>59</v>
+        <v>53</v>
       </c>
     </row>
     <row r="63" spans="1:2">
       <c r="A63" t="s">
-        <v>60</v>
-      </c>
-      <c r="B63">
-        <v>2</v>
+        <v>54</v>
       </c>
     </row>
     <row r="64" spans="1:2">
       <c r="A64" t="s">
-        <v>61</v>
-      </c>
-      <c r="B64">
-        <v>1</v>
+        <v>55</v>
       </c>
     </row>
     <row r="65" spans="1:2">
       <c r="A65" t="s">
-        <v>62</v>
-      </c>
-      <c r="B65" s="1" t="s">
-        <v>37</v>
+        <v>56</v>
       </c>
     </row>
     <row r="66" spans="1:2">
       <c r="A66" t="s">
-        <v>63</v>
+        <v>57</v>
+      </c>
+      <c r="B66" s="1" t="s">
+        <v>37</v>
       </c>
     </row>
     <row r="67" spans="1:2">
       <c r="A67" t="s">
-        <v>64</v>
+        <v>58</v>
       </c>
     </row>
     <row r="68" spans="1:2">
       <c r="A68" t="s">
-        <v>65</v>
+        <v>59</v>
       </c>
     </row>
     <row r="69" spans="1:2">
       <c r="A69" t="s">
-        <v>66</v>
-      </c>
-      <c r="B69" s="1" t="s">
-        <v>37</v>
+        <v>60</v>
+      </c>
+      <c r="B69">
+        <v>2</v>
       </c>
     </row>
     <row r="70" spans="1:2">
       <c r="A70" t="s">
-        <v>67</v>
+        <v>61</v>
       </c>
       <c r="B70">
-        <v>2500</v>
+        <v>1</v>
       </c>
     </row>
     <row r="71" spans="1:2">
       <c r="A71" t="s">
-        <v>68</v>
-      </c>
-      <c r="B71">
-        <v>4500</v>
+        <v>62</v>
+      </c>
+      <c r="B71" s="1" t="s">
+        <v>37</v>
       </c>
     </row>
     <row r="72" spans="1:2">
       <c r="A72" t="s">
-        <v>69</v>
-      </c>
-      <c r="B72" s="1" t="s">
-        <v>37</v>
+        <v>63</v>
       </c>
     </row>
     <row r="73" spans="1:2">
       <c r="A73" t="s">
-        <v>70</v>
-      </c>
-      <c r="B73" s="1" t="s">
-        <v>113</v>
+        <v>64</v>
       </c>
     </row>
     <row r="74" spans="1:2">
       <c r="A74" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="75" spans="1:2">
+      <c r="A75" t="s">
+        <v>66</v>
+      </c>
+      <c r="B75" s="1" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="76" spans="1:2">
+      <c r="A76" t="s">
+        <v>67</v>
+      </c>
+      <c r="B76">
+        <v>2500</v>
+      </c>
+    </row>
+    <row r="77" spans="1:2">
+      <c r="A77" t="s">
+        <v>68</v>
+      </c>
+      <c r="B77">
+        <v>4500</v>
+      </c>
+    </row>
+    <row r="78" spans="1:2">
+      <c r="A78" t="s">
+        <v>69</v>
+      </c>
+      <c r="B78" s="1" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="79" spans="1:2">
+      <c r="A79" t="s">
+        <v>70</v>
+      </c>
+      <c r="B79" s="1" t="s">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="80" spans="1:2">
+      <c r="A80" t="s">
         <v>111</v>
       </c>
-      <c r="B74" t="s">
+      <c r="B80" t="s">
         <v>112</v>
       </c>
     </row>

--- a/data/gravel/Esker Lorax Ti 2025.xlsx
+++ b/data/gravel/Esker Lorax Ti 2025.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11026"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11122"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/walker/Documents/Github/Bike Geometry Project/data/gravel/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{634AE11E-D668-FE4E-94B1-954B54314412}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1DF48488-F5F9-CA4C-9340-730E70799C06}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="7380" yWindow="500" windowWidth="20520" windowHeight="17080" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="1860" yWindow="540" windowWidth="26940" windowHeight="16840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="124" uniqueCount="120">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="127" uniqueCount="123">
   <si>
     <t>brand</t>
   </si>
@@ -248,9 +248,6 @@
     <t>currency</t>
   </si>
   <si>
-    <t>a8:f33</t>
-  </si>
-  <si>
     <t>class</t>
   </si>
   <si>
@@ -362,9 +359,6 @@
     <t>effectively equal to rigid fork of this length</t>
   </si>
   <si>
-    <t>suspension</t>
-  </si>
-  <si>
     <t>https://eskercycles.com/cdn/shop/files/Lorax_Rigid_Ti_3_5_25_0013_1.jpg?v=1741577688&amp;width=3840</t>
   </si>
   <si>
@@ -393,6 +387,21 @@
   </si>
   <si>
     <t>fork_material</t>
+  </si>
+  <si>
+    <t>fork_travel</t>
+  </si>
+  <si>
+    <t>fork_sag</t>
+  </si>
+  <si>
+    <t>rigid</t>
+  </si>
+  <si>
+    <t>carbon</t>
+  </si>
+  <si>
+    <t>a8:f35</t>
   </si>
 </sst>
 </file>
@@ -782,7 +791,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:G80"/>
+  <dimension ref="A1:G82"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="20"/>
   <cols>
     <col min="1" max="2" width="19.6640625" customWidth="1"/>
@@ -793,7 +802,7 @@
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
     </row>
     <row r="2" spans="1:6">
@@ -801,7 +810,7 @@
         <v>1</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
     </row>
     <row r="3" spans="1:6">
@@ -825,12 +834,12 @@
         <v>5</v>
       </c>
       <c r="B5" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
     </row>
     <row r="6" spans="1:6">
       <c r="B6" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
     </row>
     <row r="7" spans="1:6" ht="22">
@@ -838,10 +847,10 @@
         <v>6</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>71</v>
+        <v>122</v>
       </c>
       <c r="C7" s="9" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
     </row>
     <row r="8" spans="1:6">
@@ -852,16 +861,16 @@
         <v>8</v>
       </c>
       <c r="C8" s="3" t="s">
+        <v>102</v>
+      </c>
+      <c r="D8" s="3" t="s">
         <v>103</v>
       </c>
-      <c r="D8" s="3" t="s">
+      <c r="E8" s="3" t="s">
         <v>104</v>
       </c>
-      <c r="E8" s="3" t="s">
+      <c r="F8" s="3" t="s">
         <v>105</v>
-      </c>
-      <c r="F8" s="3" t="s">
-        <v>106</v>
       </c>
     </row>
     <row r="9" spans="1:6">
@@ -869,7 +878,7 @@
         <v>9</v>
       </c>
       <c r="B9" s="4" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="C9" s="3">
         <v>537</v>
@@ -889,7 +898,7 @@
         <v>18</v>
       </c>
       <c r="B10" s="4" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="C10" s="3">
         <v>365</v>
@@ -909,7 +918,7 @@
         <v>17</v>
       </c>
       <c r="B11" s="4" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="C11" s="3">
         <v>600</v>
@@ -929,7 +938,7 @@
         <v>15</v>
       </c>
       <c r="B12" s="4" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="C12" s="3">
         <v>68</v>
@@ -949,7 +958,7 @@
         <v>11</v>
       </c>
       <c r="B13" s="4" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="C13" s="3">
         <v>90</v>
@@ -969,7 +978,7 @@
         <v>14</v>
       </c>
       <c r="B14" s="4" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="C14" s="3">
         <v>74</v>
@@ -989,7 +998,7 @@
         <v>10</v>
       </c>
       <c r="B15" s="4" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="C15" s="3">
         <v>400</v>
@@ -1006,10 +1015,10 @@
     </row>
     <row r="16" spans="1:6">
       <c r="A16" s="1" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="B16" s="4" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="C16" s="3">
         <v>300</v>
@@ -1029,7 +1038,7 @@
         <v>12</v>
       </c>
       <c r="B17" s="4" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="C17" s="3">
         <v>445</v>
@@ -1049,7 +1058,7 @@
         <v>16</v>
       </c>
       <c r="B18" s="6" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="C18" s="3">
         <v>44</v>
@@ -1069,7 +1078,7 @@
         <v>21</v>
       </c>
       <c r="B19" s="4" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="C19" s="3">
         <v>495</v>
@@ -1084,7 +1093,7 @@
         <v>495</v>
       </c>
       <c r="G19" s="1" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
     </row>
     <row r="20" spans="1:7">
@@ -1092,7 +1101,7 @@
         <v>13</v>
       </c>
       <c r="B20" s="4" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="C20" s="3">
         <v>68</v>
@@ -1112,7 +1121,7 @@
         <v>19</v>
       </c>
       <c r="B21" s="4" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="C21" s="3">
         <v>1075</v>
@@ -1132,7 +1141,7 @@
         <v>24</v>
       </c>
       <c r="B22" s="4" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="C22" s="3">
         <v>60</v>
@@ -1150,490 +1159,531 @@
     </row>
     <row r="23" spans="1:7">
       <c r="A23" s="1" t="s">
-        <v>101</v>
+        <v>118</v>
       </c>
       <c r="B23" s="4"/>
-      <c r="C23" s="3"/>
+      <c r="C23" s="3">
+        <v>120</v>
+      </c>
       <c r="D23" s="3">
+        <v>120</v>
+      </c>
+      <c r="E23" s="3">
+        <v>120</v>
+      </c>
+      <c r="F23" s="3">
+        <v>120</v>
+      </c>
+      <c r="G23" s="1"/>
+    </row>
+    <row r="24" spans="1:7">
+      <c r="A24" s="1" t="s">
+        <v>119</v>
+      </c>
+      <c r="B24" s="4"/>
+      <c r="C24" s="3">
+        <v>30</v>
+      </c>
+      <c r="D24" s="3">
+        <v>30</v>
+      </c>
+      <c r="E24" s="3">
+        <v>30</v>
+      </c>
+      <c r="F24" s="3">
+        <v>30</v>
+      </c>
+      <c r="G24" s="1"/>
+    </row>
+    <row r="25" spans="1:7">
+      <c r="A25" s="1" t="s">
+        <v>100</v>
+      </c>
+      <c r="B25" s="4"/>
+      <c r="C25" s="3"/>
+      <c r="D25" s="3">
         <v>2284</v>
       </c>
-      <c r="E23" s="3"/>
-      <c r="F23" s="3"/>
-      <c r="G23" s="1"/>
-    </row>
-    <row r="24" spans="1:7">
-      <c r="A24" t="s">
-        <v>20</v>
-      </c>
-      <c r="G24" s="1"/>
-    </row>
-    <row r="25" spans="1:7">
-      <c r="A25" t="s">
-        <v>22</v>
-      </c>
+      <c r="E25" s="3"/>
+      <c r="F25" s="3"/>
       <c r="G25" s="1"/>
     </row>
     <row r="26" spans="1:7">
       <c r="A26" t="s">
-        <v>23</v>
-      </c>
+        <v>20</v>
+      </c>
+      <c r="G26" s="1"/>
     </row>
     <row r="27" spans="1:7">
       <c r="A27" t="s">
-        <v>25</v>
-      </c>
+        <v>22</v>
+      </c>
+      <c r="G27" s="1"/>
     </row>
     <row r="28" spans="1:7">
       <c r="A28" t="s">
-        <v>26</v>
+        <v>23</v>
       </c>
     </row>
     <row r="29" spans="1:7">
       <c r="A29" t="s">
-        <v>27</v>
-      </c>
-      <c r="C29">
-        <v>700</v>
-      </c>
-      <c r="D29">
-        <v>700</v>
-      </c>
-      <c r="E29">
-        <v>700</v>
-      </c>
-      <c r="F29">
-        <v>700</v>
+        <v>25</v>
       </c>
     </row>
     <row r="30" spans="1:7">
       <c r="A30" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="31" spans="1:7">
+      <c r="A31" t="s">
+        <v>27</v>
+      </c>
+      <c r="C31">
+        <v>700</v>
+      </c>
+      <c r="D31">
+        <v>700</v>
+      </c>
+      <c r="E31">
+        <v>700</v>
+      </c>
+      <c r="F31">
+        <v>700</v>
+      </c>
+    </row>
+    <row r="32" spans="1:7">
+      <c r="A32" t="s">
         <v>28</v>
       </c>
-      <c r="C30">
+      <c r="C32">
         <f>2.2*25.4</f>
         <v>55.88</v>
       </c>
-      <c r="D30">
-        <f t="shared" ref="D30:F30" si="0">2.2*25.4</f>
+      <c r="D32">
+        <f t="shared" ref="D32:F32" si="0">2.2*25.4</f>
         <v>55.88</v>
       </c>
-      <c r="E30">
+      <c r="E32">
         <f t="shared" si="0"/>
         <v>55.88</v>
       </c>
-      <c r="F30">
+      <c r="F32">
         <f t="shared" si="0"/>
         <v>55.88</v>
       </c>
     </row>
-    <row r="31" spans="1:7">
-      <c r="A31" t="s">
+    <row r="33" spans="1:7">
+      <c r="A33" t="s">
         <v>29</v>
       </c>
-      <c r="C31">
+      <c r="C33">
         <f>2.6*25.4</f>
         <v>66.039999999999992</v>
       </c>
-      <c r="D31">
-        <f t="shared" ref="D31:F31" si="1">2.6*25.4</f>
+      <c r="D33">
+        <f t="shared" ref="D33:F33" si="1">2.6*25.4</f>
         <v>66.039999999999992</v>
       </c>
-      <c r="E31">
+      <c r="E33">
         <f t="shared" si="1"/>
         <v>66.039999999999992</v>
       </c>
-      <c r="F31">
+      <c r="F33">
         <f t="shared" si="1"/>
         <v>66.039999999999992</v>
       </c>
     </row>
-    <row r="32" spans="1:7">
-      <c r="A32" t="s">
+    <row r="34" spans="1:7">
+      <c r="A34" t="s">
         <v>30</v>
       </c>
-      <c r="C32">
-        <f>C34*2.54</f>
+      <c r="C34">
+        <f>C36*2.54</f>
         <v>160.02000000000001</v>
       </c>
-      <c r="D32">
-        <f>AVERAGE(D34,C35)*2.54</f>
+      <c r="D34">
+        <f>AVERAGE(D36,C37)*2.54</f>
         <v>168.91</v>
       </c>
-      <c r="E32">
-        <f t="shared" ref="E32:F32" si="2">AVERAGE(E34,D35)*2.54</f>
+      <c r="E34">
+        <f t="shared" ref="E34:F34" si="2">AVERAGE(E36,D37)*2.54</f>
         <v>176.53</v>
       </c>
-      <c r="F32">
+      <c r="F34">
         <f t="shared" si="2"/>
         <v>184.15</v>
       </c>
     </row>
-    <row r="33" spans="1:7">
-      <c r="A33" t="s">
+    <row r="35" spans="1:7">
+      <c r="A35" t="s">
         <v>31</v>
       </c>
-      <c r="C33" s="1">
-        <f>D32</f>
+      <c r="C35" s="1">
+        <f>D34</f>
         <v>168.91</v>
       </c>
-      <c r="D33" s="1">
-        <f t="shared" ref="D33:E33" si="3">E32</f>
+      <c r="D35" s="1">
+        <f t="shared" ref="D35:E35" si="3">E34</f>
         <v>176.53</v>
       </c>
-      <c r="E33" s="1">
+      <c r="E35" s="1">
         <f t="shared" si="3"/>
         <v>184.15</v>
       </c>
-      <c r="F33">
-        <f t="shared" ref="F33" si="4">F35*2.54</f>
+      <c r="F35">
+        <f t="shared" ref="F35" si="4">F37*2.54</f>
         <v>193.04</v>
       </c>
     </row>
-    <row r="34" spans="1:7">
-      <c r="C34">
+    <row r="36" spans="1:7">
+      <c r="C36">
         <v>63</v>
       </c>
-      <c r="D34">
+      <c r="D36">
         <v>66</v>
       </c>
-      <c r="E34">
+      <c r="E36">
         <v>69</v>
       </c>
-      <c r="F34">
+      <c r="F36">
         <v>72</v>
-      </c>
-    </row>
-    <row r="35" spans="1:7">
-      <c r="A35" t="s">
-        <v>32</v>
-      </c>
-      <c r="B35" t="s">
-        <v>33</v>
-      </c>
-      <c r="C35">
-        <v>67</v>
-      </c>
-      <c r="D35">
-        <v>70</v>
-      </c>
-      <c r="E35">
-        <v>73</v>
-      </c>
-      <c r="F35">
-        <v>76</v>
-      </c>
-    </row>
-    <row r="36" spans="1:7">
-      <c r="A36" t="s">
-        <v>72</v>
-      </c>
-      <c r="B36" t="s">
-        <v>73</v>
-      </c>
-      <c r="C36" s="3" t="s">
-        <v>94</v>
-      </c>
-      <c r="D36" s="3" t="s">
-        <v>95</v>
-      </c>
-      <c r="E36" s="3" t="s">
-        <v>96</v>
-      </c>
-      <c r="F36" s="3" t="s">
-        <v>97</v>
-      </c>
-      <c r="G36" s="8" t="s">
-        <v>93</v>
       </c>
     </row>
     <row r="37" spans="1:7">
       <c r="A37" t="s">
-        <v>74</v>
-      </c>
-      <c r="B37" s="1" t="s">
-        <v>99</v>
+        <v>32</v>
+      </c>
+      <c r="B37" t="s">
+        <v>33</v>
+      </c>
+      <c r="C37">
+        <v>67</v>
+      </c>
+      <c r="D37">
+        <v>70</v>
+      </c>
+      <c r="E37">
+        <v>73</v>
+      </c>
+      <c r="F37">
+        <v>76</v>
       </c>
     </row>
     <row r="38" spans="1:7">
       <c r="A38" t="s">
-        <v>75</v>
-      </c>
-      <c r="B38" s="1" t="s">
-        <v>109</v>
+        <v>71</v>
+      </c>
+      <c r="B38" t="s">
+        <v>72</v>
+      </c>
+      <c r="C38" s="3" t="s">
+        <v>93</v>
+      </c>
+      <c r="D38" s="3" t="s">
+        <v>94</v>
+      </c>
+      <c r="E38" s="3" t="s">
+        <v>95</v>
+      </c>
+      <c r="F38" s="3" t="s">
+        <v>96</v>
+      </c>
+      <c r="G38" s="8" t="s">
+        <v>92</v>
       </c>
     </row>
     <row r="39" spans="1:7">
       <c r="A39" t="s">
-        <v>34</v>
-      </c>
-      <c r="B39" t="s">
-        <v>35</v>
+        <v>73</v>
+      </c>
+      <c r="B39" s="1" t="s">
+        <v>98</v>
       </c>
     </row>
     <row r="40" spans="1:7">
       <c r="A40" t="s">
-        <v>36</v>
-      </c>
-      <c r="B40" t="s">
-        <v>37</v>
+        <v>74</v>
+      </c>
+      <c r="B40" s="1" t="s">
+        <v>120</v>
       </c>
     </row>
     <row r="41" spans="1:7">
       <c r="A41" t="s">
-        <v>38</v>
+        <v>34</v>
+      </c>
+      <c r="B41" t="s">
+        <v>35</v>
       </c>
     </row>
     <row r="42" spans="1:7">
       <c r="A42" t="s">
+        <v>36</v>
+      </c>
+      <c r="B42" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="43" spans="1:7">
+      <c r="A43" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="44" spans="1:7">
+      <c r="A44" t="s">
         <v>39</v>
       </c>
-      <c r="B42">
+      <c r="B44">
         <f>2.6*25.4</f>
         <v>66.039999999999992</v>
       </c>
     </row>
-    <row r="43" spans="1:7">
-      <c r="A43" t="s">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="44" spans="1:7">
-      <c r="A44" t="s">
-        <v>41</v>
-      </c>
-      <c r="B44">
-        <v>120</v>
-      </c>
-    </row>
     <row r="45" spans="1:7">
       <c r="A45" t="s">
-        <v>42</v>
-      </c>
-      <c r="B45" s="1">
-        <v>120</v>
+        <v>40</v>
       </c>
     </row>
     <row r="46" spans="1:7">
       <c r="A46" t="s">
-        <v>43</v>
+        <v>41</v>
+      </c>
+      <c r="B46">
+        <v>120</v>
       </c>
     </row>
     <row r="47" spans="1:7">
       <c r="A47" t="s">
-        <v>44</v>
+        <v>42</v>
+      </c>
+      <c r="B47" s="1">
+        <v>120</v>
       </c>
     </row>
     <row r="48" spans="1:7">
       <c r="A48" t="s">
-        <v>45</v>
-      </c>
-      <c r="B48">
-        <v>148</v>
+        <v>43</v>
       </c>
     </row>
     <row r="49" spans="1:2">
       <c r="A49" t="s">
-        <v>46</v>
-      </c>
-      <c r="B49">
-        <v>110</v>
+        <v>44</v>
       </c>
     </row>
     <row r="50" spans="1:2">
       <c r="A50" t="s">
-        <v>114</v>
+        <v>45</v>
+      </c>
+      <c r="B50">
+        <v>148</v>
       </c>
     </row>
     <row r="51" spans="1:2">
       <c r="A51" t="s">
-        <v>115</v>
+        <v>46</v>
+      </c>
+      <c r="B51">
+        <v>110</v>
       </c>
     </row>
     <row r="52" spans="1:2">
       <c r="A52" t="s">
-        <v>116</v>
+        <v>112</v>
       </c>
     </row>
     <row r="53" spans="1:2">
       <c r="A53" t="s">
-        <v>117</v>
+        <v>113</v>
       </c>
     </row>
     <row r="54" spans="1:2">
       <c r="A54" t="s">
-        <v>118</v>
+        <v>114</v>
       </c>
     </row>
     <row r="55" spans="1:2">
       <c r="A55" t="s">
-        <v>119</v>
+        <v>115</v>
       </c>
     </row>
     <row r="56" spans="1:2">
       <c r="A56" t="s">
-        <v>47</v>
-      </c>
-      <c r="B56" s="1" t="s">
-        <v>107</v>
+        <v>116</v>
       </c>
     </row>
     <row r="57" spans="1:2">
       <c r="A57" t="s">
-        <v>48</v>
+        <v>117</v>
+      </c>
+      <c r="B57" s="1" t="s">
+        <v>121</v>
       </c>
     </row>
     <row r="58" spans="1:2">
       <c r="A58" t="s">
-        <v>49</v>
-      </c>
-      <c r="B58">
-        <v>31.6</v>
+        <v>47</v>
+      </c>
+      <c r="B58" s="1" t="s">
+        <v>106</v>
       </c>
     </row>
     <row r="59" spans="1:2">
       <c r="A59" t="s">
-        <v>50</v>
-      </c>
-      <c r="B59" s="1" t="s">
-        <v>102</v>
+        <v>48</v>
       </c>
     </row>
     <row r="60" spans="1:2">
       <c r="A60" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="B60">
-        <v>38</v>
+        <v>31.6</v>
       </c>
     </row>
     <row r="61" spans="1:2">
       <c r="A61" t="s">
-        <v>52</v>
+        <v>50</v>
+      </c>
+      <c r="B61" s="1" t="s">
+        <v>101</v>
       </c>
     </row>
     <row r="62" spans="1:2">
       <c r="A62" t="s">
-        <v>53</v>
+        <v>51</v>
+      </c>
+      <c r="B62">
+        <v>38</v>
       </c>
     </row>
     <row r="63" spans="1:2">
       <c r="A63" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
     </row>
     <row r="64" spans="1:2">
       <c r="A64" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
     </row>
     <row r="65" spans="1:2">
       <c r="A65" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
     </row>
     <row r="66" spans="1:2">
       <c r="A66" t="s">
-        <v>57</v>
-      </c>
-      <c r="B66" s="1" t="s">
-        <v>37</v>
+        <v>55</v>
       </c>
     </row>
     <row r="67" spans="1:2">
       <c r="A67" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
     </row>
     <row r="68" spans="1:2">
       <c r="A68" t="s">
-        <v>59</v>
+        <v>57</v>
+      </c>
+      <c r="B68" s="1" t="s">
+        <v>37</v>
       </c>
     </row>
     <row r="69" spans="1:2">
       <c r="A69" t="s">
-        <v>60</v>
-      </c>
-      <c r="B69">
-        <v>2</v>
+        <v>58</v>
       </c>
     </row>
     <row r="70" spans="1:2">
       <c r="A70" t="s">
-        <v>61</v>
-      </c>
-      <c r="B70">
-        <v>1</v>
+        <v>59</v>
       </c>
     </row>
     <row r="71" spans="1:2">
       <c r="A71" t="s">
-        <v>62</v>
-      </c>
-      <c r="B71" s="1" t="s">
-        <v>37</v>
+        <v>60</v>
+      </c>
+      <c r="B71">
+        <v>2</v>
       </c>
     </row>
     <row r="72" spans="1:2">
       <c r="A72" t="s">
-        <v>63</v>
+        <v>61</v>
+      </c>
+      <c r="B72">
+        <v>1</v>
       </c>
     </row>
     <row r="73" spans="1:2">
       <c r="A73" t="s">
-        <v>64</v>
+        <v>62</v>
+      </c>
+      <c r="B73" s="1" t="s">
+        <v>37</v>
       </c>
     </row>
     <row r="74" spans="1:2">
       <c r="A74" t="s">
-        <v>65</v>
+        <v>63</v>
       </c>
     </row>
     <row r="75" spans="1:2">
       <c r="A75" t="s">
-        <v>66</v>
-      </c>
-      <c r="B75" s="1" t="s">
-        <v>37</v>
+        <v>64</v>
       </c>
     </row>
     <row r="76" spans="1:2">
       <c r="A76" t="s">
-        <v>67</v>
-      </c>
-      <c r="B76">
-        <v>2500</v>
+        <v>65</v>
       </c>
     </row>
     <row r="77" spans="1:2">
       <c r="A77" t="s">
-        <v>68</v>
-      </c>
-      <c r="B77">
-        <v>4500</v>
+        <v>66</v>
+      </c>
+      <c r="B77" s="1" t="s">
+        <v>37</v>
       </c>
     </row>
     <row r="78" spans="1:2">
       <c r="A78" t="s">
-        <v>69</v>
-      </c>
-      <c r="B78" s="1" t="s">
-        <v>37</v>
+        <v>67</v>
+      </c>
+      <c r="B78">
+        <v>2500</v>
       </c>
     </row>
     <row r="79" spans="1:2">
       <c r="A79" t="s">
-        <v>70</v>
-      </c>
-      <c r="B79" s="1" t="s">
-        <v>113</v>
+        <v>68</v>
+      </c>
+      <c r="B79">
+        <v>4500</v>
       </c>
     </row>
     <row r="80" spans="1:2">
       <c r="A80" t="s">
+        <v>69</v>
+      </c>
+      <c r="B80" s="1" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="81" spans="1:2">
+      <c r="A81" t="s">
+        <v>70</v>
+      </c>
+      <c r="B81" s="1" t="s">
         <v>111</v>
       </c>
-      <c r="B80" t="s">
-        <v>112</v>
+    </row>
+    <row r="82" spans="1:2">
+      <c r="A82" t="s">
+        <v>109</v>
+      </c>
+      <c r="B82" t="s">
+        <v>110</v>
       </c>
     </row>
   </sheetData>

--- a/data/gravel/Esker Lorax Ti 2025.xlsx
+++ b/data/gravel/Esker Lorax Ti 2025.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/walker/Documents/Github/Bike Geometry Project/data/gravel/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1DF48488-F5F9-CA4C-9340-730E70799C06}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{94F60120-ADE0-A849-B5DB-95DA9DBF3145}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="1860" yWindow="540" windowWidth="26940" windowHeight="16840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="127" uniqueCount="123">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="129" uniqueCount="125">
   <si>
     <t>brand</t>
   </si>
@@ -395,13 +395,19 @@
     <t>fork_sag</t>
   </si>
   <si>
-    <t>rigid</t>
-  </si>
-  <si>
     <t>carbon</t>
   </si>
   <si>
     <t>a8:f35</t>
+  </si>
+  <si>
+    <t>ZS44</t>
+  </si>
+  <si>
+    <t>EC44</t>
+  </si>
+  <si>
+    <t>suspension</t>
   </si>
 </sst>
 </file>
@@ -797,7 +803,7 @@
     <col min="1" max="2" width="19.6640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6">
+    <row r="1" spans="1:7">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -805,7 +811,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="2" spans="1:6">
+    <row r="2" spans="1:7">
       <c r="A2" t="s">
         <v>1</v>
       </c>
@@ -813,7 +819,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="3" spans="1:6">
+    <row r="3" spans="1:7">
       <c r="A3" t="s">
         <v>2</v>
       </c>
@@ -821,7 +827,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="4" spans="1:6">
+    <row r="4" spans="1:7">
       <c r="A4" t="s">
         <v>4</v>
       </c>
@@ -829,7 +835,7 @@
         <v>45882</v>
       </c>
     </row>
-    <row r="5" spans="1:6">
+    <row r="5" spans="1:7">
       <c r="A5" t="s">
         <v>5</v>
       </c>
@@ -837,23 +843,20 @@
         <v>77</v>
       </c>
     </row>
-    <row r="6" spans="1:6">
+    <row r="6" spans="1:7">
       <c r="B6" t="s">
         <v>108</v>
       </c>
     </row>
-    <row r="7" spans="1:6" ht="22">
+    <row r="7" spans="1:7">
       <c r="A7" t="s">
         <v>6</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>122</v>
-      </c>
-      <c r="C7" s="9" t="s">
-        <v>97</v>
-      </c>
-    </row>
-    <row r="8" spans="1:6">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="8" spans="1:7">
       <c r="A8" t="s">
         <v>7</v>
       </c>
@@ -873,7 +876,7 @@
         <v>105</v>
       </c>
     </row>
-    <row r="9" spans="1:6">
+    <row r="9" spans="1:7" ht="22">
       <c r="A9" t="s">
         <v>9</v>
       </c>
@@ -892,8 +895,11 @@
       <c r="F9" s="5">
         <v>610</v>
       </c>
-    </row>
-    <row r="10" spans="1:6">
+      <c r="G9" s="9" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="10" spans="1:7">
       <c r="A10" t="s">
         <v>18</v>
       </c>
@@ -913,7 +919,7 @@
         <v>405</v>
       </c>
     </row>
-    <row r="11" spans="1:6">
+    <row r="11" spans="1:7">
       <c r="A11" t="s">
         <v>17</v>
       </c>
@@ -933,7 +939,7 @@
         <v>670</v>
       </c>
     </row>
-    <row r="12" spans="1:6">
+    <row r="12" spans="1:7">
       <c r="A12" t="s">
         <v>15</v>
       </c>
@@ -953,7 +959,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="13" spans="1:6">
+    <row r="13" spans="1:7">
       <c r="A13" t="s">
         <v>11</v>
       </c>
@@ -973,7 +979,7 @@
         <v>165</v>
       </c>
     </row>
-    <row r="14" spans="1:6">
+    <row r="14" spans="1:7">
       <c r="A14" t="s">
         <v>14</v>
       </c>
@@ -993,7 +999,7 @@
         <v>73</v>
       </c>
     </row>
-    <row r="15" spans="1:6">
+    <row r="15" spans="1:7">
       <c r="A15" t="s">
         <v>10</v>
       </c>
@@ -1013,7 +1019,7 @@
         <v>560</v>
       </c>
     </row>
-    <row r="16" spans="1:6">
+    <row r="16" spans="1:7">
       <c r="A16" s="1" t="s">
         <v>99</v>
       </c>
@@ -1406,7 +1412,7 @@
         <v>74</v>
       </c>
       <c r="B40" s="1" t="s">
-        <v>120</v>
+        <v>124</v>
       </c>
     </row>
     <row r="41" spans="1:7">
@@ -1495,11 +1501,17 @@
       <c r="A53" t="s">
         <v>113</v>
       </c>
+      <c r="B53" s="1" t="s">
+        <v>122</v>
+      </c>
     </row>
     <row r="54" spans="1:2">
       <c r="A54" t="s">
         <v>114</v>
       </c>
+      <c r="B54" s="1" t="s">
+        <v>123</v>
+      </c>
     </row>
     <row r="55" spans="1:2">
       <c r="A55" t="s">
@@ -1516,7 +1528,7 @@
         <v>117</v>
       </c>
       <c r="B57" s="1" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
     </row>
     <row r="58" spans="1:2">

--- a/data/gravel/Esker Lorax Ti 2025.xlsx
+++ b/data/gravel/Esker Lorax Ti 2025.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11122"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10308"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/walker/Documents/Github/Bike Geometry Project/data/gravel/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{94F60120-ADE0-A849-B5DB-95DA9DBF3145}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9E98244E-D98B-A240-90D5-6F5462310F5C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="1860" yWindow="540" windowWidth="26940" windowHeight="16840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
